--- a/reductions/data/acidification_dat_extra.xlsx
+++ b/reductions/data/acidification_dat_extra.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aarhusuniversitet-my.sharepoint.com/personal/au583430_uni_au_dk/Documents/Documents/GitHub/GD-NH3/reductions/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="406" documentId="8_{35EDC6DB-B444-4E75-9EC7-B91B9DC064D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56513FF2-93B8-41C4-B69D-71F839A9D28D}"/>
+  <xr:revisionPtr revIDLastSave="409" documentId="8_{35EDC6DB-B444-4E75-9EC7-B91B9DC064D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{065AE67C-0A4B-4D0C-A35A-119D2959127F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-45" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Acidification_NH3_reduction_dat" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="91">
   <si>
     <t>Untreated</t>
   </si>
@@ -1154,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y96"/>
+  <dimension ref="A1:Y93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.28515625" bestFit="1" customWidth="1"/>
@@ -1164,227 +1164,263 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" t="s">
+        <v>32</v>
+      </c>
       <c r="J1" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="K1" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L1" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M1" t="s">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="N1" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="O1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="P1" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="Q1" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="R1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T1" t="s">
+        <v>43</v>
+      </c>
+      <c r="U1" t="s">
+        <v>44</v>
+      </c>
+      <c r="V1" t="s">
+        <v>87</v>
+      </c>
+      <c r="W1" t="s">
+        <v>88</v>
+      </c>
+      <c r="X1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2">
+        <v>101</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2">
         <v>2</v>
       </c>
-      <c r="S1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T1" t="s">
-        <v>0</v>
-      </c>
-      <c r="U1" t="s">
-        <v>1</v>
-      </c>
-      <c r="V1" t="s">
-        <v>0</v>
-      </c>
-      <c r="W1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J2">
+        <v>23.5</v>
+      </c>
+      <c r="K2">
+        <v>7.1</v>
+      </c>
+      <c r="L2">
+        <v>91.4</v>
+      </c>
+      <c r="M2">
+        <v>2.16</v>
+      </c>
+      <c r="P2">
+        <v>21.9</v>
+      </c>
+      <c r="Q2">
+        <v>6.6</v>
+      </c>
+      <c r="R2">
+        <v>91.5</v>
+      </c>
+      <c r="S2">
+        <v>2.16</v>
+      </c>
+      <c r="T2">
+        <v>26.9</v>
+      </c>
+      <c r="U2">
+        <v>25</v>
+      </c>
+      <c r="X2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3">
+        <v>101</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3">
         <v>4</v>
       </c>
-      <c r="G2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="G3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J3">
+        <v>23.5</v>
+      </c>
+      <c r="K3">
+        <v>7.1</v>
+      </c>
+      <c r="L3">
+        <v>91.4</v>
+      </c>
+      <c r="M3">
+        <v>2.16</v>
+      </c>
+      <c r="P3">
+        <v>22.4</v>
+      </c>
+      <c r="Q3">
         <v>6</v>
       </c>
-      <c r="I2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" t="s">
-        <v>11</v>
-      </c>
-      <c r="N2" t="s">
-        <v>12</v>
-      </c>
-      <c r="O2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R2" t="s">
-        <v>10</v>
-      </c>
-      <c r="S2" t="s">
-        <v>11</v>
-      </c>
-      <c r="T2" t="s">
-        <v>15</v>
-      </c>
-      <c r="U2" t="s">
-        <v>16</v>
-      </c>
-      <c r="V2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W2" t="s">
-        <v>16</v>
-      </c>
-      <c r="X2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="J3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O3" t="s">
-        <v>22</v>
-      </c>
-      <c r="P3" t="s">
-        <v>23</v>
-      </c>
-      <c r="R3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S3" t="s">
-        <v>20</v>
-      </c>
-      <c r="T3" t="s">
-        <v>24</v>
-      </c>
-      <c r="U3" t="s">
-        <v>24</v>
-      </c>
-      <c r="V3" t="s">
-        <v>86</v>
-      </c>
-      <c r="W3" t="s">
-        <v>86</v>
-      </c>
-      <c r="X3" t="s">
-        <v>25</v>
+      <c r="R3">
+        <v>93.1</v>
+      </c>
+      <c r="S3">
+        <v>2.19</v>
+      </c>
+      <c r="T3">
+        <v>26.9</v>
+      </c>
+      <c r="U3">
+        <v>18.3</v>
+      </c>
+      <c r="X3">
+        <v>0.32</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
+        <v>46</v>
+      </c>
+      <c r="B4">
+        <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4">
         <v>2</v>
       </c>
-      <c r="F4" t="s">
-        <v>29</v>
-      </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="I4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" t="s">
-        <v>36</v>
-      </c>
-      <c r="N4" t="s">
-        <v>37</v>
-      </c>
-      <c r="O4" t="s">
-        <v>38</v>
-      </c>
-      <c r="P4" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>40</v>
-      </c>
-      <c r="R4" t="s">
-        <v>41</v>
-      </c>
-      <c r="S4" t="s">
-        <v>42</v>
-      </c>
-      <c r="T4" t="s">
-        <v>43</v>
-      </c>
-      <c r="U4" t="s">
-        <v>44</v>
-      </c>
-      <c r="V4" t="s">
-        <v>87</v>
-      </c>
-      <c r="W4" t="s">
-        <v>88</v>
-      </c>
-      <c r="X4" t="s">
-        <v>45</v>
+        <v>52</v>
+      </c>
+      <c r="J4">
+        <v>21.3</v>
+      </c>
+      <c r="K4">
+        <v>7.1</v>
+      </c>
+      <c r="L4">
+        <v>90.3</v>
+      </c>
+      <c r="M4">
+        <v>2.11</v>
+      </c>
+      <c r="P4">
+        <v>19.8</v>
+      </c>
+      <c r="Q4">
+        <v>6.6</v>
+      </c>
+      <c r="R4">
+        <v>84.3</v>
+      </c>
+      <c r="S4">
+        <v>1.98</v>
+      </c>
+      <c r="T4">
+        <v>30.1</v>
+      </c>
+      <c r="U4">
+        <v>26.5</v>
+      </c>
+      <c r="X4">
+        <v>0.12</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
@@ -1404,7 +1440,7 @@
         <v>49</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5" t="s">
         <v>50</v>
@@ -1416,37 +1452,37 @@
         <v>52</v>
       </c>
       <c r="J5">
-        <v>23.5</v>
+        <v>21.3</v>
       </c>
       <c r="K5">
         <v>7.1</v>
       </c>
       <c r="L5">
-        <v>91.4</v>
+        <v>90.3</v>
       </c>
       <c r="M5">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="P5">
-        <v>21.9</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="Q5">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="R5">
-        <v>91.5</v>
+        <v>85.7</v>
       </c>
       <c r="S5">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="T5">
-        <v>26.9</v>
+        <v>30.1</v>
       </c>
       <c r="U5">
-        <v>25</v>
+        <v>24.7</v>
       </c>
       <c r="X5">
-        <v>7.0000000000000007E-2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
@@ -1466,7 +1502,7 @@
         <v>49</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6" t="s">
         <v>50</v>
@@ -1478,37 +1514,37 @@
         <v>52</v>
       </c>
       <c r="J6">
-        <v>23.5</v>
+        <v>21.6</v>
       </c>
       <c r="K6">
+        <v>7.2</v>
+      </c>
+      <c r="L6">
+        <v>80.8</v>
+      </c>
+      <c r="M6">
+        <v>1.89</v>
+      </c>
+      <c r="P6">
+        <v>19.8</v>
+      </c>
+      <c r="Q6">
         <v>7.1</v>
       </c>
-      <c r="L6">
-        <v>91.4</v>
-      </c>
-      <c r="M6">
-        <v>2.16</v>
-      </c>
-      <c r="P6">
-        <v>22.4</v>
-      </c>
-      <c r="Q6">
-        <v>6</v>
-      </c>
       <c r="R6">
-        <v>93.1</v>
+        <v>80</v>
       </c>
       <c r="S6">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="T6">
-        <v>26.9</v>
+        <v>45.1</v>
       </c>
       <c r="U6">
-        <v>18.3</v>
+        <v>43.9</v>
       </c>
       <c r="X6">
-        <v>0.32</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
@@ -1528,7 +1564,7 @@
         <v>49</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G7" t="s">
         <v>50</v>
@@ -1540,37 +1576,37 @@
         <v>52</v>
       </c>
       <c r="J7">
-        <v>21.3</v>
+        <v>21.6</v>
       </c>
       <c r="K7">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="L7">
-        <v>90.3</v>
+        <v>80.8</v>
       </c>
       <c r="M7">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="P7">
-        <v>19.8</v>
+        <v>20.2</v>
       </c>
       <c r="Q7">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="R7">
-        <v>84.3</v>
+        <v>81.7</v>
       </c>
       <c r="S7">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="T7">
-        <v>30.1</v>
+        <v>45.1</v>
       </c>
       <c r="U7">
-        <v>26.5</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="X7">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
@@ -1590,7 +1626,7 @@
         <v>49</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8" t="s">
         <v>50</v>
@@ -1602,37 +1638,37 @@
         <v>52</v>
       </c>
       <c r="J8">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="K8">
         <v>7.1</v>
       </c>
       <c r="L8">
-        <v>90.3</v>
+        <v>83</v>
       </c>
       <c r="M8">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="P8">
-        <v>19.899999999999999</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="Q8">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="R8">
-        <v>85.7</v>
+        <v>82.8</v>
       </c>
       <c r="S8">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="T8">
-        <v>30.1</v>
+        <v>38.4</v>
       </c>
       <c r="U8">
-        <v>24.7</v>
+        <v>36.4</v>
       </c>
       <c r="X8">
-        <v>0.18</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
@@ -1652,7 +1688,7 @@
         <v>49</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G9" t="s">
         <v>50</v>
@@ -1664,223 +1700,232 @@
         <v>52</v>
       </c>
       <c r="J9">
-        <v>21.6</v>
+        <v>20.9</v>
       </c>
       <c r="K9">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="L9">
-        <v>80.8</v>
+        <v>83</v>
       </c>
       <c r="M9">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="P9">
-        <v>19.8</v>
+        <v>20.6</v>
       </c>
       <c r="Q9">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="R9">
-        <v>80</v>
+        <v>83.8</v>
       </c>
       <c r="S9">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="T9">
-        <v>45.1</v>
+        <v>38.4</v>
       </c>
       <c r="U9">
-        <v>43.9</v>
+        <v>31</v>
       </c>
       <c r="X9">
-        <v>0.03</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B10">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
         <v>49</v>
       </c>
-      <c r="F10">
-        <v>4</v>
-      </c>
       <c r="G10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H10" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="I10" t="s">
         <v>52</v>
       </c>
       <c r="J10">
-        <v>21.6</v>
+        <v>31.4</v>
       </c>
       <c r="K10">
-        <v>7.2</v>
+        <v>6.83</v>
       </c>
       <c r="L10">
-        <v>80.8</v>
+        <v>56.2</v>
       </c>
       <c r="M10">
-        <v>1.89</v>
+        <v>3.64</v>
+      </c>
+      <c r="N10">
+        <v>5.4</v>
+      </c>
+      <c r="O10">
+        <v>4.9000000000000004</v>
       </c>
       <c r="P10">
-        <v>20.2</v>
+        <v>37.4</v>
       </c>
       <c r="Q10">
-        <v>6.5</v>
+        <v>5.89</v>
       </c>
       <c r="R10">
-        <v>81.7</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="S10">
-        <v>1.93</v>
+        <v>2.58</v>
       </c>
       <c r="T10">
-        <v>45.1</v>
+        <v>20.5</v>
       </c>
       <c r="U10">
-        <v>32.799999999999997</v>
+        <v>7.5</v>
       </c>
       <c r="X10">
-        <v>0.27</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B11">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
         <v>49</v>
       </c>
-      <c r="F11">
-        <v>2</v>
-      </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H11" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="I11" t="s">
         <v>52</v>
       </c>
       <c r="J11">
-        <v>20.9</v>
+        <v>31.4</v>
       </c>
       <c r="K11">
-        <v>7.1</v>
+        <v>6.81</v>
       </c>
       <c r="L11">
-        <v>83</v>
+        <v>59.4</v>
       </c>
       <c r="M11">
-        <v>2.02</v>
+        <v>3.74</v>
+      </c>
+      <c r="N11">
+        <v>5.4</v>
+      </c>
+      <c r="O11">
+        <v>4.9000000000000004</v>
       </c>
       <c r="P11">
-        <v>20.399999999999999</v>
+        <v>37.4</v>
       </c>
       <c r="Q11">
-        <v>7</v>
+        <v>5.82</v>
       </c>
       <c r="R11">
-        <v>82.8</v>
+        <v>36.6</v>
       </c>
       <c r="S11">
-        <v>1.98</v>
+        <v>2.63</v>
       </c>
       <c r="T11">
-        <v>38.4</v>
+        <v>19</v>
       </c>
       <c r="U11">
-        <v>36.4</v>
+        <v>5.3</v>
       </c>
       <c r="X11">
-        <v>0.05</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B12">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
         <v>49</v>
       </c>
-      <c r="F12">
-        <v>4</v>
-      </c>
       <c r="G12" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H12" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="I12" t="s">
         <v>52</v>
       </c>
       <c r="J12">
-        <v>20.9</v>
+        <v>31.4</v>
       </c>
       <c r="K12">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="L12">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="M12">
-        <v>2.02</v>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="N12">
+        <v>6.3</v>
+      </c>
+      <c r="O12">
+        <v>4</v>
       </c>
       <c r="P12">
-        <v>20.6</v>
+        <v>37.4</v>
       </c>
       <c r="Q12">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="R12">
-        <v>83.8</v>
+        <v>39</v>
       </c>
       <c r="S12">
-        <v>2</v>
+        <v>4.03</v>
       </c>
       <c r="T12">
-        <v>38.4</v>
+        <v>17</v>
       </c>
       <c r="U12">
-        <v>31</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="X12">
-        <v>0.19</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
@@ -1894,13 +1939,13 @@
         <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E13" t="s">
         <v>49</v>
       </c>
       <c r="G13" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="H13" t="s">
         <v>57</v>
@@ -1912,40 +1957,40 @@
         <v>31.4</v>
       </c>
       <c r="K13">
-        <v>6.83</v>
+        <v>7.2</v>
       </c>
       <c r="L13">
-        <v>56.2</v>
+        <v>57</v>
       </c>
       <c r="M13">
-        <v>3.64</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N13">
-        <v>5.4</v>
+        <v>6.3</v>
       </c>
       <c r="O13">
-        <v>4.9000000000000004</v>
+        <v>4</v>
       </c>
       <c r="P13">
-        <v>37.4</v>
+        <v>31.4</v>
       </c>
       <c r="Q13">
-        <v>5.89</v>
+        <v>6.2</v>
       </c>
       <c r="R13">
-        <v>37.200000000000003</v>
+        <v>59</v>
       </c>
       <c r="S13">
-        <v>2.58</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="T13">
-        <v>20.5</v>
+        <v>17</v>
       </c>
       <c r="U13">
-        <v>7.5</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="X13">
-        <v>0.63</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -1959,13 +2004,13 @@
         <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
         <v>49</v>
       </c>
       <c r="G14" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="H14" t="s">
         <v>57</v>
@@ -1977,40 +2022,40 @@
         <v>31.4</v>
       </c>
       <c r="K14">
-        <v>6.81</v>
+        <v>7.2</v>
       </c>
       <c r="L14">
-        <v>59.4</v>
+        <v>57</v>
       </c>
       <c r="M14">
-        <v>3.74</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N14">
-        <v>5.4</v>
+        <v>6.3</v>
       </c>
       <c r="O14">
-        <v>4.9000000000000004</v>
+        <v>4</v>
       </c>
       <c r="P14">
-        <v>37.4</v>
+        <v>31.4</v>
       </c>
       <c r="Q14">
-        <v>5.82</v>
+        <v>6.2</v>
       </c>
       <c r="R14">
-        <v>36.6</v>
+        <v>60</v>
       </c>
       <c r="S14">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="T14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="U14">
-        <v>5.3</v>
+        <v>10.1</v>
       </c>
       <c r="X14">
-        <v>0.72</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
@@ -2024,13 +2069,13 @@
         <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E15" t="s">
         <v>49</v>
       </c>
       <c r="G15" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="H15" t="s">
         <v>57</v>
@@ -2042,40 +2087,40 @@
         <v>31.4</v>
       </c>
       <c r="K15">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="L15">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="M15">
-        <v>4.0999999999999996</v>
+        <v>2.8</v>
       </c>
       <c r="N15">
-        <v>6.3</v>
+        <v>12.4</v>
       </c>
       <c r="O15">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P15">
-        <v>37.4</v>
+        <v>31.4</v>
       </c>
       <c r="Q15">
-        <v>5.9</v>
+        <v>6.7</v>
       </c>
       <c r="R15">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="S15">
-        <v>4.03</v>
+        <v>2.9</v>
       </c>
       <c r="T15">
-        <v>17</v>
+        <v>34.6</v>
       </c>
       <c r="U15">
-        <v>4.4000000000000004</v>
+        <v>29.2</v>
       </c>
       <c r="X15">
-        <v>0.74</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
@@ -2107,40 +2152,40 @@
         <v>31.4</v>
       </c>
       <c r="K16">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="L16">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="M16">
-        <v>4.0999999999999996</v>
+        <v>2.9</v>
       </c>
       <c r="N16">
-        <v>6.3</v>
+        <v>12.4</v>
       </c>
       <c r="O16">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P16">
         <v>31.4</v>
       </c>
       <c r="Q16">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="R16">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="S16">
-        <v>4.0999999999999996</v>
+        <v>2.7</v>
       </c>
       <c r="T16">
-        <v>17</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="U16">
-        <v>8.1999999999999993</v>
+        <v>22.2</v>
       </c>
       <c r="X16">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
@@ -2154,13 +2199,13 @@
         <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E17" t="s">
         <v>49</v>
       </c>
       <c r="G17" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H17" t="s">
         <v>57</v>
@@ -2172,40 +2217,40 @@
         <v>31.4</v>
       </c>
       <c r="K17">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="L17">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="M17">
-        <v>4.0999999999999996</v>
+        <v>2.66</v>
       </c>
       <c r="N17">
-        <v>6.3</v>
+        <v>3.7</v>
       </c>
       <c r="O17">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P17">
-        <v>31.4</v>
+        <v>37.4</v>
       </c>
       <c r="Q17">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="R17">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="S17">
-        <v>4</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="T17">
-        <v>17</v>
+        <v>41.2</v>
       </c>
       <c r="U17">
-        <v>10.1</v>
+        <v>18.2</v>
       </c>
       <c r="X17">
-        <v>0.41</v>
+        <v>0.56000000000000005</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
@@ -2219,13 +2264,13 @@
         <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E18" t="s">
         <v>49</v>
       </c>
       <c r="G18" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H18" t="s">
         <v>57</v>
@@ -2237,40 +2282,40 @@
         <v>31.4</v>
       </c>
       <c r="K18">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="L18">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="M18">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="N18">
-        <v>12.4</v>
+        <v>3.7</v>
       </c>
       <c r="O18">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P18">
-        <v>31.4</v>
+        <v>37.4</v>
       </c>
       <c r="Q18">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="R18">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="S18">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="T18">
-        <v>34.6</v>
+        <v>41.2</v>
       </c>
       <c r="U18">
-        <v>29.2</v>
+        <v>15.5</v>
       </c>
       <c r="X18">
-        <v>0.16</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
@@ -2302,40 +2347,40 @@
         <v>31.4</v>
       </c>
       <c r="K19">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="L19">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="M19">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="N19">
-        <v>12.4</v>
+        <v>3.7</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P19">
         <v>31.4</v>
       </c>
       <c r="Q19">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="R19">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="S19">
-        <v>2.7</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="T19">
-        <v>36.799999999999997</v>
+        <v>41.2</v>
       </c>
       <c r="U19">
-        <v>22.2</v>
+        <v>27.1</v>
       </c>
       <c r="X19">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
@@ -2349,13 +2394,13 @@
         <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E20" t="s">
         <v>49</v>
       </c>
       <c r="G20" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="H20" t="s">
         <v>57</v>
@@ -2367,40 +2412,40 @@
         <v>31.4</v>
       </c>
       <c r="K20">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="L20">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="M20">
-        <v>2.66</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="N20">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="O20">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="P20">
-        <v>37.4</v>
+        <v>31.4</v>
       </c>
       <c r="Q20">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="R20">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="S20">
         <v>2.2999999999999998</v>
       </c>
       <c r="T20">
-        <v>41.2</v>
+        <v>40.4</v>
       </c>
       <c r="U20">
-        <v>18.2</v>
+        <v>15.7</v>
       </c>
       <c r="X20">
-        <v>0.56000000000000005</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
@@ -2414,13 +2459,13 @@
         <v>54</v>
       </c>
       <c r="D21" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E21" t="s">
         <v>49</v>
       </c>
       <c r="G21" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="H21" t="s">
         <v>57</v>
@@ -2432,40 +2477,40 @@
         <v>31.4</v>
       </c>
       <c r="K21">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="L21">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="M21">
-        <v>2.66</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="N21">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="O21">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="P21">
-        <v>37.4</v>
+        <v>31.4</v>
       </c>
       <c r="Q21">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="R21">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="S21">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="T21">
-        <v>41.2</v>
+        <v>40.4</v>
       </c>
       <c r="U21">
-        <v>15.5</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="X21">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
@@ -2479,13 +2524,13 @@
         <v>54</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E22" t="s">
         <v>49</v>
       </c>
       <c r="G22" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H22" t="s">
         <v>57</v>
@@ -2497,235 +2542,205 @@
         <v>31.4</v>
       </c>
       <c r="K22">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="L22">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="M22">
-        <v>2.66</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="N22">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="O22">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="P22">
-        <v>31.4</v>
+        <v>37.4</v>
       </c>
       <c r="Q22">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="R22">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="S22">
-        <v>2.2999999999999998</v>
+        <v>1.4</v>
       </c>
       <c r="T22">
-        <v>41.2</v>
+        <v>40.4</v>
       </c>
       <c r="U22">
-        <v>27.1</v>
+        <v>17.7</v>
       </c>
       <c r="X22">
-        <v>0.34</v>
+        <v>0.56000000000000005</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B23">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D23" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
-      </c>
-      <c r="G23" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H23" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I23" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J23">
-        <v>31.4</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>7.8</v>
-      </c>
-      <c r="L23">
-        <v>67</v>
+        <v>7.5</v>
       </c>
       <c r="M23">
-        <v>2.2000000000000002</v>
+        <v>2.7</v>
       </c>
       <c r="N23">
-        <v>2.8</v>
-      </c>
-      <c r="O23">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="P23">
-        <v>31.4</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>6.5</v>
-      </c>
-      <c r="R23">
-        <v>48</v>
+        <v>4.5</v>
       </c>
       <c r="S23">
-        <v>2.2999999999999998</v>
+        <v>3.3</v>
       </c>
       <c r="T23">
-        <v>40.4</v>
+        <v>28.5</v>
       </c>
       <c r="U23">
-        <v>15.7</v>
+        <v>0.4</v>
       </c>
       <c r="X23">
-        <v>0.61</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B24">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E24" t="s">
-        <v>49</v>
-      </c>
-      <c r="G24" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H24" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I24" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J24">
-        <v>31.4</v>
+        <v>10</v>
       </c>
       <c r="K24">
-        <v>7.8</v>
-      </c>
-      <c r="L24">
-        <v>67</v>
+        <v>7.5</v>
       </c>
       <c r="M24">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
       <c r="N24">
-        <v>2.8</v>
-      </c>
-      <c r="O24">
-        <v>2.8</v>
+        <v>21.9</v>
       </c>
       <c r="P24">
-        <v>31.4</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>6.6</v>
-      </c>
-      <c r="R24">
-        <v>48</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="S24">
         <v>2.1</v>
       </c>
       <c r="T24">
-        <v>40.4</v>
+        <v>97.9</v>
       </c>
       <c r="U24">
-        <v>19.100000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="X24">
-        <v>0.53</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B25">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C25" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E25" t="s">
-        <v>49</v>
-      </c>
-      <c r="G25" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H25" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="I25" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J25">
-        <v>31.4</v>
+        <v>6.5</v>
       </c>
       <c r="K25">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="L25">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="M25">
-        <v>2.2000000000000002</v>
+        <v>3.54</v>
       </c>
       <c r="N25">
-        <v>2.8</v>
-      </c>
-      <c r="O25">
-        <v>2.8</v>
+        <v>13</v>
       </c>
       <c r="P25">
-        <v>37.4</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>6.3</v>
+        <v>3.9</v>
       </c>
       <c r="R25">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="S25">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="T25">
-        <v>40.4</v>
+        <v>42.3</v>
       </c>
       <c r="U25">
-        <v>17.7</v>
+        <v>2.6</v>
       </c>
       <c r="X25">
-        <v>0.56000000000000005</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
@@ -2745,40 +2760,46 @@
         <v>60</v>
       </c>
       <c r="H26" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I26" t="s">
         <v>62</v>
       </c>
       <c r="J26">
-        <v>10</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="K26">
         <v>7.5</v>
       </c>
+      <c r="L26">
+        <v>73</v>
+      </c>
       <c r="M26">
-        <v>2.7</v>
+        <v>2.16</v>
       </c>
       <c r="N26">
-        <v>4.5</v>
+        <v>12.2</v>
       </c>
       <c r="P26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
       </c>
+      <c r="R26">
+        <v>111</v>
+      </c>
       <c r="S26">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="T26">
-        <v>28.5</v>
+        <v>58.3</v>
       </c>
       <c r="U26">
-        <v>0.4</v>
+        <v>11.1</v>
       </c>
       <c r="X26">
-        <v>0.99</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
@@ -2798,40 +2819,46 @@
         <v>60</v>
       </c>
       <c r="H27" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I27" t="s">
         <v>62</v>
       </c>
       <c r="J27">
-        <v>10</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="K27">
-        <v>7.5</v>
+        <v>7.1</v>
+      </c>
+      <c r="L27">
+        <v>83</v>
       </c>
       <c r="M27">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="N27">
-        <v>21.9</v>
+        <v>12.3</v>
       </c>
       <c r="P27">
-        <v>10</v>
+        <v>8.1</v>
       </c>
       <c r="Q27">
-        <v>5.0999999999999996</v>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="R27">
+        <v>116</v>
       </c>
       <c r="S27">
         <v>2.1</v>
       </c>
       <c r="T27">
-        <v>97.9</v>
+        <v>44.2</v>
       </c>
       <c r="U27">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="X27">
-        <v>0.87</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
@@ -2851,46 +2878,46 @@
         <v>60</v>
       </c>
       <c r="H28" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I28" t="s">
         <v>62</v>
       </c>
       <c r="J28">
-        <v>6.5</v>
+        <v>9.9</v>
       </c>
       <c r="K28">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="L28">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M28">
-        <v>3.54</v>
+        <v>2.35</v>
       </c>
       <c r="N28">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P28">
-        <v>7</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="Q28">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="R28">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="S28">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="T28">
-        <v>42.3</v>
+        <v>33.9</v>
       </c>
       <c r="U28">
-        <v>2.6</v>
+        <v>0.2</v>
       </c>
       <c r="X28">
-        <v>0.94</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
@@ -2910,46 +2937,46 @@
         <v>60</v>
       </c>
       <c r="H29" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I29" t="s">
         <v>62</v>
       </c>
       <c r="J29">
-        <v>10.199999999999999</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="K29">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="L29">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="M29">
-        <v>2.16</v>
+        <v>2.35</v>
       </c>
       <c r="N29">
-        <v>12.2</v>
+        <v>19.2</v>
       </c>
       <c r="P29">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Q29">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="R29">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="S29">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="T29">
-        <v>58.3</v>
+        <v>51.1</v>
       </c>
       <c r="U29">
-        <v>11.1</v>
+        <v>7</v>
       </c>
       <c r="X29">
-        <v>0.81</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
@@ -2969,46 +2996,46 @@
         <v>60</v>
       </c>
       <c r="H30" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I30" t="s">
         <v>62</v>
       </c>
       <c r="J30">
-        <v>9.8000000000000007</v>
+        <v>12.7</v>
       </c>
       <c r="K30">
         <v>7.1</v>
       </c>
       <c r="L30">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="M30">
-        <v>2.35</v>
+        <v>1.57</v>
       </c>
       <c r="N30">
-        <v>12.3</v>
+        <v>20.3</v>
       </c>
       <c r="P30">
-        <v>8.1</v>
+        <v>13.2</v>
       </c>
       <c r="Q30">
-        <v>4.5999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="R30">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="S30">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="T30">
-        <v>44.2</v>
+        <v>52</v>
       </c>
       <c r="U30">
-        <v>13.5</v>
+        <v>7</v>
       </c>
       <c r="X30">
-        <v>0.69</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
@@ -3028,46 +3055,46 @@
         <v>60</v>
       </c>
       <c r="H31" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I31" t="s">
         <v>62</v>
       </c>
       <c r="J31">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="K31">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="L31">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="M31">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="N31">
-        <v>12</v>
+        <v>15.7</v>
       </c>
       <c r="P31">
-        <v>8.6999999999999993</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="Q31">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="R31">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="S31">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="T31">
-        <v>33.9</v>
+        <v>49.7</v>
       </c>
       <c r="U31">
-        <v>0.2</v>
+        <v>13.2</v>
       </c>
       <c r="X31">
-        <v>0.99</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
@@ -3087,46 +3114,46 @@
         <v>60</v>
       </c>
       <c r="H32" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I32" t="s">
         <v>62</v>
       </c>
       <c r="J32">
-        <v>9.8000000000000007</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="K32">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="L32">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="M32">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="N32">
-        <v>19.2</v>
+        <v>13.5</v>
       </c>
       <c r="P32">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
       <c r="Q32">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="R32">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="S32">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="T32">
-        <v>51.1</v>
+        <v>58.1</v>
       </c>
       <c r="U32">
-        <v>7</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="X32">
-        <v>0.86</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
@@ -3146,46 +3173,46 @@
         <v>60</v>
       </c>
       <c r="H33" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I33" t="s">
         <v>62</v>
       </c>
       <c r="J33">
-        <v>12.7</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="K33">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="L33">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M33">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="N33">
-        <v>20.3</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="P33">
-        <v>13.2</v>
+        <v>10.1</v>
       </c>
       <c r="Q33">
-        <v>4.4000000000000004</v>
+        <v>6</v>
       </c>
       <c r="R33">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="S33">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="T33">
-        <v>52</v>
+        <v>96.7</v>
       </c>
       <c r="U33">
-        <v>7</v>
+        <v>46.5</v>
       </c>
       <c r="X33">
-        <v>0.87</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
@@ -3205,46 +3232,46 @@
         <v>60</v>
       </c>
       <c r="H34" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I34" t="s">
         <v>62</v>
       </c>
       <c r="J34">
-        <v>9.6</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="K34">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="L34">
+        <v>72</v>
+      </c>
+      <c r="M34">
+        <v>1.53</v>
+      </c>
+      <c r="N34">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="P34">
+        <v>10.3</v>
+      </c>
+      <c r="Q34">
+        <v>5.8</v>
+      </c>
+      <c r="R34">
         <v>76</v>
       </c>
-      <c r="M34">
-        <v>2.4</v>
-      </c>
-      <c r="N34">
-        <v>15.7</v>
-      </c>
-      <c r="P34">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="Q34">
-        <v>4.5</v>
-      </c>
-      <c r="R34">
-        <v>81</v>
-      </c>
       <c r="S34">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>49.7</v>
+        <v>96.7</v>
       </c>
       <c r="U34">
-        <v>13.2</v>
+        <v>47.8</v>
       </c>
       <c r="X34">
-        <v>0.73</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
@@ -3264,46 +3291,46 @@
         <v>60</v>
       </c>
       <c r="H35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I35" t="s">
         <v>62</v>
       </c>
       <c r="J35">
-        <v>8.6999999999999993</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="K35">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="L35">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M35">
-        <v>2.41</v>
+        <v>1.53</v>
       </c>
       <c r="N35">
-        <v>13.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="P35">
-        <v>7.7</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="Q35">
-        <v>5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="R35">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="S35">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="T35">
-        <v>58.1</v>
+        <v>96.7</v>
       </c>
       <c r="U35">
-        <v>20.399999999999999</v>
+        <v>20.6</v>
       </c>
       <c r="X35">
-        <v>0.65</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
@@ -3323,46 +3350,46 @@
         <v>60</v>
       </c>
       <c r="H36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I36" t="s">
         <v>62</v>
       </c>
       <c r="J36">
-        <v>9.8000000000000007</v>
+        <v>17.3</v>
       </c>
       <c r="K36">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="L36">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="M36">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="N36">
-        <v>16.399999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="P36">
-        <v>10.1</v>
+        <v>14.9</v>
       </c>
       <c r="Q36">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="R36">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="S36">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="T36">
-        <v>96.7</v>
+        <v>85.8</v>
       </c>
       <c r="U36">
-        <v>46.5</v>
+        <v>60.5</v>
       </c>
       <c r="X36">
-        <v>0.52</v>
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
@@ -3382,46 +3409,46 @@
         <v>60</v>
       </c>
       <c r="H37" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I37" t="s">
         <v>62</v>
       </c>
       <c r="J37">
-        <v>9.8000000000000007</v>
+        <v>17.3</v>
       </c>
       <c r="K37">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="L37">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="M37">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="N37">
-        <v>16.399999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="P37">
-        <v>10.3</v>
+        <v>16.7</v>
       </c>
       <c r="Q37">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="R37">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="S37">
         <v>1.3</v>
       </c>
       <c r="T37">
-        <v>96.7</v>
+        <v>85.8</v>
       </c>
       <c r="U37">
-        <v>47.8</v>
+        <v>29.5</v>
       </c>
       <c r="X37">
-        <v>0.51</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
@@ -3441,46 +3468,46 @@
         <v>60</v>
       </c>
       <c r="H38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I38" t="s">
         <v>62</v>
       </c>
       <c r="J38">
-        <v>9.8000000000000007</v>
+        <v>17.3</v>
       </c>
       <c r="K38">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="L38">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="M38">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="N38">
-        <v>16.399999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="P38">
-        <v>10.199999999999999</v>
+        <v>15.1</v>
       </c>
       <c r="Q38">
-        <v>4.9000000000000004</v>
+        <v>5.8</v>
       </c>
       <c r="R38">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="S38">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T38">
-        <v>96.7</v>
+        <v>85.8</v>
       </c>
       <c r="U38">
-        <v>20.6</v>
+        <v>13.5</v>
       </c>
       <c r="X38">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
@@ -3500,46 +3527,46 @@
         <v>60</v>
       </c>
       <c r="H39" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I39" t="s">
         <v>62</v>
       </c>
       <c r="J39">
-        <v>17.3</v>
+        <v>11.6</v>
       </c>
       <c r="K39">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="L39">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="M39">
-        <v>1.21</v>
+        <v>1.72</v>
       </c>
       <c r="N39">
-        <v>7.4</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="P39">
-        <v>14.9</v>
+        <v>13</v>
       </c>
       <c r="Q39">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="R39">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="S39">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="T39">
-        <v>85.8</v>
+        <v>88.9</v>
       </c>
       <c r="U39">
-        <v>60.5</v>
+        <v>46.1</v>
       </c>
       <c r="X39">
-        <v>0.28999999999999998</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.25">
@@ -3559,46 +3586,46 @@
         <v>60</v>
       </c>
       <c r="H40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I40" t="s">
         <v>62</v>
       </c>
       <c r="J40">
-        <v>17.3</v>
+        <v>11.6</v>
       </c>
       <c r="K40">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="L40">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="M40">
-        <v>1.21</v>
+        <v>1.72</v>
       </c>
       <c r="N40">
-        <v>7.4</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="P40">
-        <v>16.7</v>
+        <v>12</v>
       </c>
       <c r="Q40">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="R40">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="S40">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="T40">
-        <v>85.8</v>
+        <v>88.9</v>
       </c>
       <c r="U40">
-        <v>29.5</v>
+        <v>41.3</v>
       </c>
       <c r="X40">
-        <v>0.66</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
@@ -3618,46 +3645,46 @@
         <v>60</v>
       </c>
       <c r="H41" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I41" t="s">
         <v>62</v>
       </c>
       <c r="J41">
-        <v>17.3</v>
+        <v>11.6</v>
       </c>
       <c r="K41">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="L41">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="M41">
-        <v>1.21</v>
+        <v>1.72</v>
       </c>
       <c r="N41">
-        <v>7.4</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="P41">
-        <v>15.1</v>
+        <v>15.8</v>
       </c>
       <c r="Q41">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="R41">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="S41">
         <v>1.5</v>
       </c>
       <c r="T41">
-        <v>85.8</v>
+        <v>88.9</v>
       </c>
       <c r="U41">
-        <v>13.5</v>
+        <v>38</v>
       </c>
       <c r="X41">
-        <v>0.84</v>
+        <v>0.56999999999999995</v>
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
@@ -3677,46 +3704,43 @@
         <v>60</v>
       </c>
       <c r="H42" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I42" t="s">
         <v>62</v>
       </c>
       <c r="J42">
-        <v>11.6</v>
+        <v>14.8</v>
       </c>
       <c r="K42">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="L42">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="M42">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="N42">
-        <v>19.100000000000001</v>
+        <v>4</v>
       </c>
       <c r="P42">
-        <v>13</v>
+        <v>10.6</v>
       </c>
       <c r="Q42">
-        <v>5.7</v>
-      </c>
-      <c r="R42">
-        <v>91</v>
+        <v>4.5</v>
       </c>
       <c r="S42">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="T42">
-        <v>88.9</v>
+        <v>21</v>
       </c>
       <c r="U42">
-        <v>46.1</v>
+        <v>1.5</v>
       </c>
       <c r="X42">
-        <v>0.48</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.25">
@@ -3736,46 +3760,43 @@
         <v>60</v>
       </c>
       <c r="H43" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I43" t="s">
         <v>62</v>
       </c>
       <c r="J43">
-        <v>11.6</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="K43">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="L43">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="M43">
-        <v>1.72</v>
+        <v>2.94</v>
       </c>
       <c r="N43">
-        <v>19.100000000000001</v>
+        <v>12</v>
       </c>
       <c r="P43">
-        <v>12</v>
+        <v>9.9</v>
       </c>
       <c r="Q43">
-        <v>5.6</v>
-      </c>
-      <c r="R43">
-        <v>93</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="S43">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="T43">
-        <v>88.9</v>
+        <v>82</v>
       </c>
       <c r="U43">
-        <v>41.3</v>
+        <v>9</v>
       </c>
       <c r="X43">
-        <v>0.54</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.25">
@@ -3795,46 +3816,43 @@
         <v>60</v>
       </c>
       <c r="H44" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I44" t="s">
         <v>62</v>
       </c>
       <c r="J44">
-        <v>11.6</v>
+        <v>22</v>
       </c>
       <c r="K44">
         <v>6.8</v>
       </c>
       <c r="L44">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="M44">
-        <v>1.72</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="N44">
-        <v>19.100000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="P44">
-        <v>15.8</v>
+        <v>22</v>
       </c>
       <c r="Q44">
-        <v>5.2</v>
-      </c>
-      <c r="R44">
-        <v>96</v>
+        <v>4.5</v>
       </c>
       <c r="S44">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T44">
-        <v>88.9</v>
+        <v>90</v>
       </c>
       <c r="U44">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="X44">
-        <v>0.56999999999999995</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.25">
@@ -3854,43 +3872,43 @@
         <v>60</v>
       </c>
       <c r="H45" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I45" t="s">
         <v>62</v>
       </c>
       <c r="J45">
-        <v>14.8</v>
+        <v>22</v>
       </c>
       <c r="K45">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="L45">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="M45">
-        <v>1.82</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="N45">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="P45">
-        <v>10.6</v>
+        <v>22</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
       </c>
       <c r="S45">
-        <v>3.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="T45">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="U45">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="X45">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.25">
@@ -3910,43 +3928,43 @@
         <v>60</v>
       </c>
       <c r="H46" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I46" t="s">
         <v>62</v>
       </c>
       <c r="J46">
-        <v>10.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="K46">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="L46">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="M46">
-        <v>2.94</v>
+        <v>0.83</v>
       </c>
       <c r="N46">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="P46">
-        <v>9.9</v>
+        <v>30</v>
       </c>
       <c r="Q46">
-        <v>5.0999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="S46">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="T46">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="U46">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="X46">
-        <v>0.89</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
@@ -3966,7 +3984,7 @@
         <v>60</v>
       </c>
       <c r="H47" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I47" t="s">
         <v>62</v>
@@ -3984,7 +4002,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="N47">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="P47">
         <v>22</v>
@@ -3993,16 +4011,16 @@
         <v>4.5</v>
       </c>
       <c r="S47">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="T47">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="U47">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="X47">
-        <v>0.97</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.25">
@@ -4022,13 +4040,13 @@
         <v>60</v>
       </c>
       <c r="H48" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I48" t="s">
         <v>62</v>
       </c>
       <c r="J48">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K48">
         <v>6.8</v>
@@ -4037,28 +4055,28 @@
         <v>108</v>
       </c>
       <c r="M48">
-        <v>1.1399999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="N48">
-        <v>5.5</v>
+        <v>12.2</v>
       </c>
       <c r="P48">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="Q48">
         <v>4.5</v>
       </c>
       <c r="S48">
-        <v>1.1000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="T48">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="U48">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="X48">
-        <v>0.89</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.25">
@@ -4078,7 +4096,7 @@
         <v>60</v>
       </c>
       <c r="H49" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I49" t="s">
         <v>62</v>
@@ -4096,7 +4114,7 @@
         <v>0.83</v>
       </c>
       <c r="N49">
-        <v>7.6</v>
+        <v>14.2</v>
       </c>
       <c r="P49">
         <v>30</v>
@@ -4108,13 +4126,13 @@
         <v>0.8</v>
       </c>
       <c r="T49">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="U49">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="X49">
-        <v>0.49</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.25">
@@ -4134,13 +4152,13 @@
         <v>60</v>
       </c>
       <c r="H50" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I50" t="s">
         <v>62</v>
       </c>
       <c r="J50">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K50">
         <v>6.8</v>
@@ -4149,28 +4167,28 @@
         <v>108</v>
       </c>
       <c r="M50">
-        <v>1.1399999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="N50">
-        <v>8.6</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="P50">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
       </c>
       <c r="S50">
-        <v>1.1000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="T50">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="U50">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="X50">
-        <v>0.6</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.25">
@@ -4190,7 +4208,7 @@
         <v>60</v>
       </c>
       <c r="H51" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I51" t="s">
         <v>62</v>
@@ -4208,7 +4226,7 @@
         <v>0.83</v>
       </c>
       <c r="N51">
-        <v>12.2</v>
+        <v>17.5</v>
       </c>
       <c r="P51">
         <v>30</v>
@@ -4220,182 +4238,113 @@
         <v>0.8</v>
       </c>
       <c r="T51">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="U51">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="X51">
-        <v>0.45</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="B52">
-        <v>104</v>
-      </c>
-      <c r="C52" t="s">
-        <v>47</v>
+        <v>114</v>
       </c>
       <c r="D52" t="s">
         <v>59</v>
       </c>
       <c r="E52" t="s">
-        <v>60</v>
-      </c>
-      <c r="H52" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="I52" t="s">
         <v>62</v>
       </c>
-      <c r="J52">
-        <v>30</v>
-      </c>
       <c r="K52">
-        <v>6.8</v>
-      </c>
-      <c r="L52">
-        <v>108</v>
-      </c>
-      <c r="M52">
-        <v>0.83</v>
-      </c>
-      <c r="N52">
-        <v>14.2</v>
-      </c>
-      <c r="P52">
-        <v>30</v>
+        <v>7.5</v>
       </c>
       <c r="Q52">
-        <v>4.5</v>
-      </c>
-      <c r="S52">
-        <v>0.8</v>
-      </c>
-      <c r="T52">
-        <v>74</v>
-      </c>
-      <c r="U52">
-        <v>14</v>
-      </c>
-      <c r="X52">
-        <v>0.81</v>
-      </c>
+        <v>6.5</v>
+      </c>
+      <c r="V52">
+        <v>3.6</v>
+      </c>
+      <c r="W52">
+        <v>0.5</v>
+      </c>
+      <c r="X52" s="1">
+        <v>0.86111111111111116</v>
+      </c>
+      <c r="Y52" s="1"/>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="B53">
-        <v>104</v>
-      </c>
-      <c r="C53" t="s">
-        <v>47</v>
+        <v>114</v>
       </c>
       <c r="D53" t="s">
         <v>59</v>
       </c>
       <c r="E53" t="s">
-        <v>60</v>
-      </c>
-      <c r="H53" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="I53" t="s">
         <v>62</v>
       </c>
-      <c r="J53">
-        <v>30</v>
-      </c>
       <c r="K53">
-        <v>6.8</v>
-      </c>
-      <c r="L53">
-        <v>108</v>
-      </c>
-      <c r="M53">
-        <v>0.83</v>
-      </c>
-      <c r="N53">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="P53">
-        <v>30</v>
+        <v>7.5</v>
       </c>
       <c r="Q53">
-        <v>4.5</v>
-      </c>
-      <c r="S53">
-        <v>0.8</v>
-      </c>
-      <c r="T53">
-        <v>62</v>
-      </c>
-      <c r="U53">
-        <v>15</v>
-      </c>
-      <c r="X53">
-        <v>0.76</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="V53">
+        <v>3.6</v>
+      </c>
+      <c r="W53">
+        <v>0.1</v>
+      </c>
+      <c r="X53" s="1">
+        <v>0.9722222222222221</v>
+      </c>
+      <c r="Y53" s="1"/>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="B54">
-        <v>104</v>
-      </c>
-      <c r="C54" t="s">
-        <v>47</v>
+        <v>114</v>
       </c>
       <c r="D54" t="s">
         <v>59</v>
       </c>
       <c r="E54" t="s">
-        <v>60</v>
-      </c>
-      <c r="H54" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="I54" t="s">
         <v>62</v>
       </c>
-      <c r="J54">
-        <v>30</v>
-      </c>
       <c r="K54">
-        <v>6.8</v>
-      </c>
-      <c r="L54">
-        <v>108</v>
-      </c>
-      <c r="M54">
-        <v>0.83</v>
-      </c>
-      <c r="N54">
-        <v>17.5</v>
-      </c>
-      <c r="P54">
-        <v>30</v>
+        <v>7.5</v>
       </c>
       <c r="Q54">
-        <v>4.5</v>
-      </c>
-      <c r="S54">
-        <v>0.8</v>
-      </c>
-      <c r="T54">
-        <v>58</v>
-      </c>
-      <c r="U54">
-        <v>20</v>
-      </c>
-      <c r="X54">
-        <v>0.66</v>
-      </c>
+        <v>6.5</v>
+      </c>
+      <c r="V54">
+        <v>2.1</v>
+      </c>
+      <c r="W54">
+        <v>0.3</v>
+      </c>
+      <c r="X54" s="1">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="Y54" s="1"/>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
@@ -4417,16 +4366,16 @@
         <v>7.5</v>
       </c>
       <c r="Q55">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="V55">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="W55">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="X55" s="1">
-        <v>0.86111111111111116</v>
+        <v>0.95238095238095222</v>
       </c>
       <c r="Y55" s="1"/>
     </row>
@@ -4450,16 +4399,16 @@
         <v>7.5</v>
       </c>
       <c r="Q56">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V56">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="W56">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="X56" s="1">
-        <v>0.9722222222222221</v>
+        <v>0.76923076923076916</v>
       </c>
       <c r="Y56" s="1"/>
     </row>
@@ -4483,16 +4432,16 @@
         <v>7.5</v>
       </c>
       <c r="Q57">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="V57">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="W57">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="X57" s="1">
-        <v>0.8571428571428571</v>
+        <v>0.92307692307692302</v>
       </c>
       <c r="Y57" s="1"/>
     </row>
@@ -4516,16 +4465,16 @@
         <v>7.5</v>
       </c>
       <c r="Q58">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V58">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="W58">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="X58" s="1">
-        <v>0.95238095238095222</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="Y58" s="1"/>
     </row>
@@ -4549,16 +4498,16 @@
         <v>7.5</v>
       </c>
       <c r="Q59">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="V59">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="W59">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="X59" s="1">
-        <v>0.76923076923076916</v>
+        <v>0.96666666666666667</v>
       </c>
       <c r="Y59" s="1"/>
     </row>
@@ -4582,16 +4531,16 @@
         <v>7.5</v>
       </c>
       <c r="Q60">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V60">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="W60">
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="X60" s="1">
-        <v>0.92307692307692302</v>
+        <v>0.78125</v>
       </c>
       <c r="Y60" s="1"/>
     </row>
@@ -4615,16 +4564,16 @@
         <v>7.5</v>
       </c>
       <c r="Q61">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="V61">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="W61">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="X61" s="1">
-        <v>0.8666666666666667</v>
+        <v>0.9375</v>
       </c>
       <c r="Y61" s="1"/>
     </row>
@@ -4648,16 +4597,16 @@
         <v>7.5</v>
       </c>
       <c r="Q62">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V62">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="W62">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="X62" s="1">
-        <v>0.96666666666666667</v>
+        <v>0.625</v>
       </c>
       <c r="Y62" s="1"/>
     </row>
@@ -4681,16 +4630,16 @@
         <v>7.5</v>
       </c>
       <c r="Q63">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="V63">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="W63">
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="X63" s="1">
-        <v>0.78125</v>
+        <v>0.875</v>
       </c>
       <c r="Y63" s="1"/>
     </row>
@@ -4714,16 +4663,16 @@
         <v>7.5</v>
       </c>
       <c r="Q64">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V64">
         <v>1.6</v>
       </c>
       <c r="W64">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="X64" s="1">
-        <v>0.9375</v>
+        <v>0.75000000000000011</v>
       </c>
       <c r="Y64" s="1"/>
     </row>
@@ -4747,16 +4696,16 @@
         <v>7.5</v>
       </c>
       <c r="Q65">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="V65">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="W65">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="X65" s="1">
-        <v>0.625</v>
+        <v>0.9375</v>
       </c>
       <c r="Y65" s="1"/>
     </row>
@@ -4780,16 +4729,16 @@
         <v>7.5</v>
       </c>
       <c r="Q66">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V66">
         <v>0.8</v>
       </c>
       <c r="W66">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="X66" s="1">
-        <v>0.875</v>
+        <v>0.625</v>
       </c>
       <c r="Y66" s="1"/>
     </row>
@@ -4813,16 +4762,16 @@
         <v>7.5</v>
       </c>
       <c r="Q67">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="V67">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="W67">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="X67" s="1">
-        <v>0.75000000000000011</v>
+        <v>0.875</v>
       </c>
       <c r="Y67" s="1"/>
     </row>
@@ -4846,16 +4795,16 @@
         <v>7.5</v>
       </c>
       <c r="Q68">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V68">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="W68">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="X68" s="1">
-        <v>0.9375</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y68" s="1"/>
     </row>
@@ -4879,16 +4828,16 @@
         <v>7.5</v>
       </c>
       <c r="Q69">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="V69">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W69">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="X69" s="1">
-        <v>0.625</v>
+        <v>0.85714285714285721</v>
       </c>
       <c r="Y69" s="1"/>
     </row>
@@ -4903,27 +4852,26 @@
         <v>59</v>
       </c>
       <c r="E70" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="I70" t="s">
         <v>62</v>
       </c>
       <c r="K70">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="Q70">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="V70">
-        <v>0.8</v>
+        <v>3.36</v>
       </c>
       <c r="W70">
-        <v>0.1</v>
+        <v>2.56</v>
       </c>
       <c r="X70" s="1">
-        <v>0.875</v>
-      </c>
-      <c r="Y70" s="1"/>
+        <v>0.23809523809523805</v>
+      </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
@@ -4936,27 +4884,26 @@
         <v>59</v>
       </c>
       <c r="E71" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="I71" t="s">
         <v>62</v>
       </c>
       <c r="K71">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="Q71">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="V71">
-        <v>0.7</v>
+        <v>3.36</v>
       </c>
       <c r="W71">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="X71" s="1">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="Y71" s="1"/>
+        <v>0.43452380952380953</v>
+      </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
@@ -4969,27 +4916,26 @@
         <v>59</v>
       </c>
       <c r="E72" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="I72" t="s">
         <v>62</v>
       </c>
       <c r="K72">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="Q72">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="V72">
-        <v>0.7</v>
+        <v>3.36</v>
       </c>
       <c r="W72">
-        <v>0.1</v>
+        <v>1.22</v>
       </c>
       <c r="X72" s="1">
-        <v>0.85714285714285721</v>
-      </c>
-      <c r="Y72" s="1"/>
+        <v>0.63690476190476186</v>
+      </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
@@ -5011,16 +4957,16 @@
         <v>7.9</v>
       </c>
       <c r="Q73">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="V73">
         <v>3.36</v>
       </c>
       <c r="W73">
-        <v>2.56</v>
+        <v>0.38</v>
       </c>
       <c r="X73" s="1">
-        <v>0.23809523809523805</v>
+        <v>0.88690476190476197</v>
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.25">
@@ -5043,16 +4989,16 @@
         <v>7.9</v>
       </c>
       <c r="Q74">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="V74">
-        <v>3.36</v>
+        <v>2.61</v>
       </c>
       <c r="W74">
-        <v>1.9</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="X74" s="1">
-        <v>0.43452380952380953</v>
+        <v>6.8965517241379198E-2</v>
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.25">
@@ -5075,16 +5021,16 @@
         <v>7.9</v>
       </c>
       <c r="Q75">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="V75">
-        <v>3.36</v>
+        <v>2.61</v>
       </c>
       <c r="W75">
-        <v>1.22</v>
+        <v>1.89</v>
       </c>
       <c r="X75" s="1">
-        <v>0.63690476190476186</v>
+        <v>0.27586206896551724</v>
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.25">
@@ -5107,16 +5053,16 @@
         <v>7.9</v>
       </c>
       <c r="Q76">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="V76">
-        <v>3.36</v>
+        <v>2.61</v>
       </c>
       <c r="W76">
-        <v>0.38</v>
+        <v>1.4</v>
       </c>
       <c r="X76" s="1">
-        <v>0.88690476190476197</v>
+        <v>0.46360153256704983</v>
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.25">
@@ -5139,16 +5085,16 @@
         <v>7.9</v>
       </c>
       <c r="Q77">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="V77">
         <v>2.61</v>
       </c>
       <c r="W77">
-        <v>2.4300000000000002</v>
+        <v>0.89</v>
       </c>
       <c r="X77" s="1">
-        <v>6.8965517241379198E-2</v>
+        <v>0.65900383141762442</v>
       </c>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.25">
@@ -5171,16 +5117,16 @@
         <v>7.9</v>
       </c>
       <c r="Q78">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="V78">
-        <v>2.61</v>
+        <v>3.04</v>
       </c>
       <c r="W78">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="X78" s="1">
-        <v>0.27586206896551724</v>
+        <v>0.40460526315789475</v>
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.25">
@@ -5203,16 +5149,16 @@
         <v>7.9</v>
       </c>
       <c r="Q79">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="V79">
-        <v>2.61</v>
+        <v>3.04</v>
       </c>
       <c r="W79">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="X79" s="1">
-        <v>0.46360153256704983</v>
+        <v>0.48026315789473684</v>
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.25">
@@ -5235,16 +5181,16 @@
         <v>7.9</v>
       </c>
       <c r="Q80">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="V80">
-        <v>2.61</v>
+        <v>3.04</v>
       </c>
       <c r="W80">
-        <v>0.89</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="X80" s="1">
-        <v>0.65900383141762442</v>
+        <v>0.63157894736842102</v>
       </c>
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.25">
@@ -5267,16 +5213,16 @@
         <v>7.9</v>
       </c>
       <c r="Q81">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="V81">
         <v>3.04</v>
       </c>
       <c r="W81">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="X81" s="1">
-        <v>0.40460526315789475</v>
+        <v>0.66776315789473695</v>
       </c>
     </row>
     <row r="82" spans="1:24" x14ac:dyDescent="0.25">
@@ -5299,16 +5245,16 @@
         <v>7.9</v>
       </c>
       <c r="Q82">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="V82">
-        <v>3.04</v>
+        <v>1.64</v>
       </c>
       <c r="W82">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="X82" s="1">
-        <v>0.48026315789473684</v>
+        <v>-0.14024390243902451</v>
       </c>
     </row>
     <row r="83" spans="1:24" x14ac:dyDescent="0.25">
@@ -5331,16 +5277,16 @@
         <v>7.9</v>
       </c>
       <c r="Q83">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="V83">
-        <v>3.04</v>
+        <v>1.64</v>
       </c>
       <c r="W83">
-        <v>1.1200000000000001</v>
+        <v>1.22</v>
       </c>
       <c r="X83" s="1">
-        <v>0.63157894736842102</v>
+        <v>0.25609756097560971</v>
       </c>
     </row>
     <row r="84" spans="1:24" x14ac:dyDescent="0.25">
@@ -5363,16 +5309,16 @@
         <v>7.9</v>
       </c>
       <c r="Q84">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="V84">
-        <v>3.04</v>
+        <v>1.64</v>
       </c>
       <c r="W84">
-        <v>1.01</v>
+        <v>0.92</v>
       </c>
       <c r="X84" s="1">
-        <v>0.66776315789473695</v>
+        <v>0.43902439024390238</v>
       </c>
     </row>
     <row r="85" spans="1:24" x14ac:dyDescent="0.25">
@@ -5395,16 +5341,16 @@
         <v>7.9</v>
       </c>
       <c r="Q85">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="V85">
         <v>1.64</v>
       </c>
       <c r="W85">
-        <v>1.87</v>
+        <v>0.48</v>
       </c>
       <c r="X85" s="1">
-        <v>-0.14024390243902451</v>
+        <v>0.70731707317073167</v>
       </c>
     </row>
     <row r="86" spans="1:24" x14ac:dyDescent="0.25">
@@ -5427,16 +5373,16 @@
         <v>7.9</v>
       </c>
       <c r="Q86">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="V86">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="W86">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="X86" s="1">
-        <v>0.25609756097560971</v>
+        <v>0.25757575757575757</v>
       </c>
     </row>
     <row r="87" spans="1:24" x14ac:dyDescent="0.25">
@@ -5459,16 +5405,16 @@
         <v>7.9</v>
       </c>
       <c r="Q87">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="V87">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="W87">
-        <v>0.92</v>
+        <v>1.96</v>
       </c>
       <c r="X87" s="1">
-        <v>0.43902439024390238</v>
+        <v>1.0101010101010111E-2</v>
       </c>
     </row>
     <row r="88" spans="1:24" x14ac:dyDescent="0.25">
@@ -5491,16 +5437,16 @@
         <v>7.9</v>
       </c>
       <c r="Q88">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="V88">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="W88">
-        <v>0.48</v>
+        <v>0.88</v>
       </c>
       <c r="X88" s="1">
-        <v>0.70731707317073167</v>
+        <v>0.55555555555555558</v>
       </c>
     </row>
     <row r="89" spans="1:24" x14ac:dyDescent="0.25">
@@ -5523,112 +5469,112 @@
         <v>7.9</v>
       </c>
       <c r="Q89">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="V89">
         <v>1.98</v>
       </c>
       <c r="W89">
-        <v>1.47</v>
+        <v>0.43</v>
       </c>
       <c r="X89" s="1">
-        <v>0.25757575757575757</v>
+        <v>0.78282828282828287</v>
       </c>
     </row>
     <row r="90" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B90">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D90" t="s">
         <v>59</v>
       </c>
       <c r="E90" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="I90" t="s">
         <v>62</v>
       </c>
       <c r="K90">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="Q90">
-        <v>7.1</v>
-      </c>
-      <c r="V90">
-        <v>1.98</v>
-      </c>
-      <c r="W90">
-        <v>1.96</v>
+        <v>5.5</v>
+      </c>
+      <c r="T90">
+        <v>64</v>
+      </c>
+      <c r="U90">
+        <v>45</v>
       </c>
       <c r="X90" s="1">
-        <v>1.0101010101010111E-2</v>
+        <v>0.296875</v>
       </c>
     </row>
     <row r="91" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B91">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D91" t="s">
         <v>59</v>
       </c>
       <c r="E91" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="I91" t="s">
         <v>62</v>
       </c>
       <c r="K91">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="Q91">
-        <v>6.8</v>
-      </c>
-      <c r="V91">
-        <v>1.98</v>
-      </c>
-      <c r="W91">
-        <v>0.88</v>
+        <v>5.5</v>
+      </c>
+      <c r="T91">
+        <v>84</v>
+      </c>
+      <c r="U91">
+        <v>57</v>
       </c>
       <c r="X91" s="1">
-        <v>0.55555555555555558</v>
+        <v>0.32142857142857145</v>
       </c>
     </row>
     <row r="92" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B92">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D92" t="s">
         <v>59</v>
       </c>
       <c r="E92" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="I92" t="s">
         <v>62</v>
       </c>
       <c r="K92">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="Q92">
-        <v>6.4</v>
-      </c>
-      <c r="V92">
-        <v>1.98</v>
-      </c>
-      <c r="W92">
-        <v>0.43</v>
+        <v>5.5</v>
+      </c>
+      <c r="T92">
+        <v>37</v>
+      </c>
+      <c r="U92">
+        <v>14</v>
       </c>
       <c r="X92" s="1">
-        <v>0.78282828282828287</v>
+        <v>0.6216216216216216</v>
       </c>
     </row>
     <row r="93" spans="1:24" x14ac:dyDescent="0.25">
@@ -5648,114 +5594,18 @@
         <v>62</v>
       </c>
       <c r="K93">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="Q93">
         <v>5.5</v>
       </c>
       <c r="T93">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="U93">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="X93" s="1">
-        <v>0.296875</v>
-      </c>
-    </row>
-    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>89</v>
-      </c>
-      <c r="B94">
-        <v>115</v>
-      </c>
-      <c r="D94" t="s">
-        <v>59</v>
-      </c>
-      <c r="E94" t="s">
-        <v>49</v>
-      </c>
-      <c r="I94" t="s">
-        <v>62</v>
-      </c>
-      <c r="K94">
-        <v>7.4</v>
-      </c>
-      <c r="Q94">
-        <v>5.5</v>
-      </c>
-      <c r="T94">
-        <v>84</v>
-      </c>
-      <c r="U94">
-        <v>57</v>
-      </c>
-      <c r="X94" s="1">
-        <v>0.32142857142857145</v>
-      </c>
-    </row>
-    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>89</v>
-      </c>
-      <c r="B95">
-        <v>115</v>
-      </c>
-      <c r="D95" t="s">
-        <v>59</v>
-      </c>
-      <c r="E95" t="s">
-        <v>49</v>
-      </c>
-      <c r="I95" t="s">
-        <v>62</v>
-      </c>
-      <c r="K95">
-        <v>7.3</v>
-      </c>
-      <c r="Q95">
-        <v>5.5</v>
-      </c>
-      <c r="T95">
-        <v>37</v>
-      </c>
-      <c r="U95">
-        <v>14</v>
-      </c>
-      <c r="X95" s="1">
-        <v>0.6216216216216216</v>
-      </c>
-    </row>
-    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>89</v>
-      </c>
-      <c r="B96">
-        <v>115</v>
-      </c>
-      <c r="D96" t="s">
-        <v>59</v>
-      </c>
-      <c r="E96" t="s">
-        <v>49</v>
-      </c>
-      <c r="I96" t="s">
-        <v>62</v>
-      </c>
-      <c r="K96">
-        <v>7.3</v>
-      </c>
-      <c r="Q96">
-        <v>5.5</v>
-      </c>
-      <c r="T96">
-        <v>31</v>
-      </c>
-      <c r="U96">
-        <v>16</v>
-      </c>
-      <c r="X96" s="1">
         <v>0.4838709677419355</v>
       </c>
     </row>
@@ -5767,11 +5617,235 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA1A3151-0061-4908-895A-C5F59267E706}">
-  <dimension ref="B2"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="J1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R1" t="s">
+        <v>2</v>
+      </c>
+      <c r="S1" t="s">
+        <v>2</v>
+      </c>
+      <c r="T1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" t="s">
+        <v>10</v>
+      </c>
+      <c r="S2" t="s">
+        <v>11</v>
+      </c>
+      <c r="T2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U2" t="s">
+        <v>16</v>
+      </c>
+      <c r="V2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W2" t="s">
+        <v>16</v>
+      </c>
+      <c r="X2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="J3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" t="s">
+        <v>86</v>
+      </c>
+      <c r="W3" t="s">
+        <v>86</v>
+      </c>
+      <c r="X3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" t="s">
+        <v>37</v>
+      </c>
+      <c r="O4" t="s">
+        <v>38</v>
+      </c>
+      <c r="P4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" t="s">
+        <v>41</v>
+      </c>
+      <c r="S4" t="s">
+        <v>42</v>
+      </c>
+      <c r="T4" t="s">
+        <v>43</v>
+      </c>
+      <c r="U4" t="s">
+        <v>44</v>
+      </c>
+      <c r="V4" t="s">
+        <v>87</v>
+      </c>
+      <c r="W4" t="s">
+        <v>88</v>
+      </c>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
         <v>90</v>
       </c>
     </row>
